--- a/output/月別集計.xlsx
+++ b/output/月別集計.xlsx
@@ -12,9 +12,9 @@
     <sheet name="元データ" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'月別集計'!$A$1:$D$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'集計明細'!$A$1:$F$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'元データ'!$A$1:$J$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'月別集計'!$A$1:$D$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'集計明細'!$A$1:$F$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'元データ'!$A$1:$J$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -461,10 +461,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -499,17 +499,193 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>25000</v>
+        <v>69000</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>25000</v>
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2026年5月</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>69000</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>2026年6月</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>69000</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026年7月</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>69000</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026年8月</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>46000</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026年9月</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>48000</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2026年10月</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>69000</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2026年11月</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>69000</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2026年12月</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>69000</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>2027年1月</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>69000</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>2027年2月</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>69000</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2027年3月</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>69000</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>23000</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D2"/>
+  <autoFilter ref="A1:D13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -520,12 +696,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -580,7 +756,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>46152</v>
+        <v>46137</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>25000</v>
@@ -591,8 +767,932 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>2026年4月</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>46137</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>U003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>2026年4月</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>46137</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>2026年5月</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>46167</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>2026年5月</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>46167</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>U003</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>2026年5月</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>46167</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>2026年6月</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>46198</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>2026年6月</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>46198</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>U003</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>2026年6月</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>46198</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>2026年7月</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>2026年7月</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>U003</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>2026年7月</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>2026年8月</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>2026年8月</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>2026年9月</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>46290</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>U003</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>2026年9月</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>46290</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>2026年10月</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>46320</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>2026年10月</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>46320</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>U003</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>2026年10月</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>46320</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>2026年11月</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>46351</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>2026年11月</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>46351</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>U003</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>2026年11月</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>46351</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>2026年12月</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>46397</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>2026年12月</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>46381</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>U003</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>2026年12月</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>46381</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>2027年1月</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>46412</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>2027年1月</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>46412</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>U003</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>2027年1月</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>46412</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>2027年2月</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>46443</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>2027年2月</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>46443</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>U003</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>2027年2月</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>46443</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>2027年3月</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>46471</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>2027年3月</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>46471</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>U003</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>2027年3月</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>46471</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F2"/>
+  <autoFilter ref="A1:F35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -603,16 +1703,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -687,7 +1787,7 @@
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>46152</v>
+        <v>46137</v>
       </c>
       <c r="E2" s="5" t="n">
         <v>25000</v>
@@ -700,7 +1800,7 @@
       <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -709,7 +1809,7 @@
         </is>
       </c>
       <c r="J2" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -729,7 +1829,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>46152</v>
+        <v>46137</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>21000</v>
@@ -742,7 +1842,7 @@
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -751,57 +1851,1447 @@
         </is>
       </c>
       <c r="J3" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
+          <t>U003</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>2026年4月</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>46137</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>2026年5月</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>46167</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>U002</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>佐藤 花子</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>2026年4月</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>46152</v>
-      </c>
-      <c r="E4" s="5" t="n">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>2026年5月</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>46167</v>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>21000</v>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>OFFICE01</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>U003</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>2026年5月</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>46167</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>2026年6月</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>46198</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>2026年6月</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>46198</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>U003</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>2026年6月</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>46198</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>2026年7月</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>2026年7月</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>U003</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>2026年7月</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>2026年8月</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>2026年8月</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>2026年9月</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>46290</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>2026年9月</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>46290</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>2026年9月</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>46290</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>重複確認用</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="b">
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>U003</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>2026年9月</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>46290</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>2026年10月</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>46320</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>2026年10月</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>46320</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>U003</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>2026年10月</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>46320</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>2026年11月</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>46351</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>2026年11月</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>46351</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>U003</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>2026年11月</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>46351</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>2026年12月</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>46397</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>対象月・支給月確認用</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="b">
         <v>1</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>2026年12月</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>46381</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>U003</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>2026年12月</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>46381</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>2027年1月</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>46412</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>2027年1月</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>46412</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>U003</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>2027年1月</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>46412</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>2027年2月</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>46443</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr"/>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>2027年2月</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>46443</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>U003</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>2027年2月</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>46443</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>U001</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>田中 太郎</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>2027年3月</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>46471</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>U002</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>佐藤 花子</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>2027年3月</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>46471</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>U003</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>鈴木 一郎</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>2027年3月</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>46471</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>23000</v>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>OFFICE01</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J4"/>
+  <autoFilter ref="A1:J37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>